--- a/cet4/result/12_职场猎人_女秘书的逆袭计划/12_职场猎人_女秘书的逆袭计划_学习版.xlsx
+++ b/cet4/result/12_职场猎人_女秘书的逆袭计划/12_职场猎人_女秘书的逆袭计划_学习版.xlsx
@@ -397,983 +397,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D53"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>masterpiece</v>
       </c>
       <c r="B2" t="str">
-        <v>masterpiece</v>
+        <v>/ˈmæstərpiːs/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>杰作</v>
       </c>
-      <c r="D2" t="str">
-        <v>masterpiece(杰作)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>wolf</v>
       </c>
       <c r="B3" t="str">
-        <v>wolf</v>
+        <v>/wʊlf/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D3" t="str">
         <v>狼</v>
       </c>
-      <c r="D3" t="str">
-        <v>wolf(狼)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>statistical</v>
       </c>
       <c r="B4" t="str">
-        <v>statistical</v>
+        <v>/stəˈtɪstɪkl/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>统计的</v>
       </c>
-      <c r="D4" t="str">
-        <v>statistical(统计的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>cargo</v>
       </c>
       <c r="B5" t="str">
-        <v>cargo</v>
+        <v>/ˈkɑːrɡoʊ/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>货物</v>
       </c>
-      <c r="D5" t="str">
-        <v>cargo(货物)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>roughly</v>
       </c>
       <c r="B6" t="str">
-        <v>roughly</v>
+        <v>/ˈrʌfli/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D6" t="str">
         <v>大致</v>
       </c>
-      <c r="D6" t="str">
-        <v>roughly(大致)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>assume</v>
       </c>
       <c r="B7" t="str">
-        <v>assume</v>
+        <v>/əˈsuːm/</v>
       </c>
       <c r="C7" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>假定</v>
       </c>
-      <c r="D7" t="str">
-        <v>assume(假定)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>French</v>
       </c>
       <c r="B8" t="str">
-        <v>French</v>
+        <v>/frentʃ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>法国</v>
       </c>
-      <c r="D8" t="str">
-        <v>French(法国)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>uncover</v>
       </c>
       <c r="B9" t="str">
-        <v>uncover</v>
+        <v>/ʌnˈkʌvər/</v>
       </c>
       <c r="C9" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>揭露</v>
       </c>
-      <c r="D9" t="str">
-        <v>uncover(揭露)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>modern</v>
       </c>
       <c r="B10" t="str">
-        <v>modern</v>
+        <v>/ˈmɑːdərn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>现代</v>
       </c>
-      <c r="D10" t="str">
-        <v>modern(现代)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>critical</v>
       </c>
       <c r="B11" t="str">
-        <v>critical</v>
+        <v>/ˈkrɪtɪkl/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>关键</v>
       </c>
-      <c r="D11" t="str">
-        <v>critical(关键)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>standard</v>
       </c>
       <c r="B12" t="str">
-        <v>standard</v>
+        <v>/ˈstændərd/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>标准</v>
       </c>
-      <c r="D12" t="str">
-        <v>standard(标准)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>trade</v>
       </c>
       <c r="B13" t="str">
-        <v>trade</v>
+        <v>/treɪd/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>贸易</v>
       </c>
-      <c r="D13" t="str">
-        <v>trade(贸易)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>disorder</v>
       </c>
       <c r="B14" t="str">
-        <v>disorder</v>
+        <v>/dɪsˈɔːrdər/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D14" t="str">
         <v>混乱</v>
       </c>
-      <c r="D14" t="str">
-        <v>disorder(混乱)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>gang</v>
       </c>
       <c r="B15" t="str">
-        <v>modern</v>
+        <v>/ɡæŋ/</v>
       </c>
       <c r="C15" t="str">
-        <v>现代</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D15" t="str">
-        <v>modern(现代)📢</v>
+        <v>帮派</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>concerning</v>
       </c>
       <c r="B16" t="str">
-        <v>gang</v>
+        <v>/kənˈsɜːrnɪŋ/</v>
       </c>
       <c r="C16" t="str">
-        <v>帮派</v>
+        <v>v./prep.</v>
       </c>
       <c r="D16" t="str">
-        <v>gang(帮派)📢</v>
+        <v>关于</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>loft</v>
       </c>
       <c r="B17" t="str">
-        <v>concerning</v>
+        <v>/lɔft/</v>
       </c>
       <c r="C17" t="str">
-        <v>关于</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D17" t="str">
-        <v>concerning(关于)📢</v>
+        <v>阁楼</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>raw</v>
       </c>
       <c r="B18" t="str">
-        <v>loft</v>
+        <v>/rɔː/</v>
       </c>
       <c r="C18" t="str">
-        <v>阁楼</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D18" t="str">
-        <v>loft(阁楼)📢</v>
+        <v>生的</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>rope</v>
       </c>
       <c r="B19" t="str">
-        <v>raw</v>
+        <v>/roʊp/</v>
       </c>
       <c r="C19" t="str">
-        <v>生的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D19" t="str">
-        <v>raw(生的)📢</v>
+        <v>绳索</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>selfish</v>
       </c>
       <c r="B20" t="str">
-        <v>rope</v>
+        <v>/ˈselfɪʃ/</v>
       </c>
       <c r="C20" t="str">
-        <v>绳索</v>
+        <v>adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>rope(绳索)📢</v>
+        <v>自私的</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>punch</v>
       </c>
       <c r="B21" t="str">
-        <v>selfish</v>
+        <v>/pʌntʃ/</v>
       </c>
       <c r="C21" t="str">
-        <v>自私的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D21" t="str">
-        <v>selfish(自私的)📢</v>
+        <v>猛击</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>hazard</v>
       </c>
       <c r="B22" t="str">
-        <v>punch</v>
+        <v>/ˈhæzərd/</v>
       </c>
       <c r="C22" t="str">
-        <v>猛击</v>
+        <v>n./vt.</v>
       </c>
       <c r="D22" t="str">
-        <v>punch(猛击)📢</v>
+        <v>危险</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>extend</v>
       </c>
       <c r="B23" t="str">
-        <v>critical</v>
+        <v>/ɪkˈstend/</v>
       </c>
       <c r="C23" t="str">
-        <v>关键</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D23" t="str">
-        <v>critical(关键)📢</v>
+        <v>延伸</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>generally</v>
       </c>
       <c r="B24" t="str">
-        <v>hazard</v>
+        <v>/ˈdʒenrəli/</v>
       </c>
       <c r="C24" t="str">
-        <v>危险</v>
+        <v>v./adv.</v>
       </c>
       <c r="D24" t="str">
-        <v>hazard(危险)📢</v>
+        <v>通常</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>wage</v>
       </c>
       <c r="B25" t="str">
-        <v>extend</v>
+        <v>/weɪdʒ/</v>
       </c>
       <c r="C25" t="str">
-        <v>延伸</v>
+        <v>n./v.</v>
       </c>
       <c r="D25" t="str">
-        <v>extend(延伸)📢</v>
+        <v>工资</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>establish</v>
       </c>
       <c r="B26" t="str">
-        <v>generally</v>
+        <v>/ɪˈstæblɪʃ/</v>
       </c>
       <c r="C26" t="str">
-        <v>通常</v>
+        <v>v.</v>
       </c>
       <c r="D26" t="str">
-        <v>generally(通常)📢</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>frame</v>
       </c>
       <c r="B27" t="str">
-        <v>wage</v>
+        <v>/freɪm/</v>
       </c>
       <c r="C27" t="str">
-        <v>工资</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>wage(工资)📢</v>
+        <v>框架</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>trouble</v>
       </c>
       <c r="B28" t="str">
-        <v>establish</v>
+        <v>/ˈtrʌbl/</v>
       </c>
       <c r="C28" t="str">
-        <v>建立</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>establish(建立)📢</v>
+        <v>麻烦</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>ministry</v>
       </c>
       <c r="B29" t="str">
-        <v>frame</v>
+        <v>/ˈmɪnɪstri/</v>
       </c>
       <c r="C29" t="str">
-        <v>框架</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>frame(框架)📢</v>
+        <v>部门</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>assure</v>
       </c>
       <c r="B30" t="str">
-        <v>trouble</v>
+        <v>/əˈʃʊr/</v>
       </c>
       <c r="C30" t="str">
-        <v>麻烦</v>
+        <v>vt.</v>
       </c>
       <c r="D30" t="str">
-        <v>trouble(麻烦)📢</v>
+        <v>保证</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>decorate</v>
       </c>
       <c r="B31" t="str">
-        <v>ministry</v>
+        <v>/ˈdekəreɪt/</v>
       </c>
       <c r="C31" t="str">
-        <v>部门</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>ministry(部门)📢</v>
+        <v>装饰</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>staff</v>
       </c>
       <c r="B32" t="str">
-        <v>assure</v>
+        <v>/stæf/</v>
       </c>
       <c r="C32" t="str">
-        <v>保证</v>
+        <v>n./vt.</v>
       </c>
       <c r="D32" t="str">
-        <v>assure(保证)📢</v>
+        <v>职员</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>react</v>
       </c>
       <c r="B33" t="str">
-        <v>decorate</v>
+        <v>/riˈækt/</v>
       </c>
       <c r="C33" t="str">
-        <v>装饰</v>
+        <v>vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>decorate(装饰)📢</v>
+        <v>反应</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>gap</v>
       </c>
       <c r="B34" t="str">
-        <v>wage</v>
+        <v>/ɡæp/</v>
       </c>
       <c r="C34" t="str">
-        <v>工资</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>wage(工资)📢</v>
+        <v>差距</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>bounce</v>
       </c>
       <c r="B35" t="str">
-        <v>staff</v>
+        <v>/baʊns/</v>
       </c>
       <c r="C35" t="str">
-        <v>职员</v>
+        <v>n./v.</v>
       </c>
       <c r="D35" t="str">
-        <v>staff(职员)📢</v>
+        <v>反弹</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>aware</v>
       </c>
       <c r="B36" t="str">
-        <v>react</v>
+        <v>/əˈwer/</v>
       </c>
       <c r="C36" t="str">
-        <v>反应</v>
+        <v>n./adj.</v>
       </c>
       <c r="D36" t="str">
-        <v>react(反应)📢</v>
+        <v>意识到的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>snowy</v>
       </c>
       <c r="B37" t="str">
-        <v>gap</v>
+        <v>/ˈsnoʊi/</v>
       </c>
       <c r="C37" t="str">
-        <v>差距</v>
+        <v>adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>gap(差距)📢</v>
+        <v>多雪的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>vine</v>
       </c>
       <c r="B38" t="str">
-        <v>bounce</v>
+        <v>/vaɪn/</v>
       </c>
       <c r="C38" t="str">
-        <v>反弹</v>
+        <v>n./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>bounce(反弹)📢</v>
+        <v>藤蔓</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>boat</v>
       </c>
       <c r="B39" t="str">
-        <v>aware</v>
+        <v>/boʊt/</v>
       </c>
       <c r="C39" t="str">
-        <v>意识到的</v>
+        <v>n./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>aware(意识到的)📢</v>
+        <v>船</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>gold</v>
       </c>
       <c r="B40" t="str">
-        <v>snowy</v>
+        <v>/ɡoʊld/</v>
       </c>
       <c r="C40" t="str">
-        <v>多雪的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>snowy(多雪的)📢</v>
+        <v>金色</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>slice</v>
       </c>
       <c r="B41" t="str">
-        <v>vine</v>
+        <v>/slaɪs/</v>
       </c>
       <c r="C41" t="str">
-        <v>藤蔓</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>vine(藤蔓)📢</v>
+        <v>切片</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>and</v>
       </c>
       <c r="B42" t="str">
-        <v>boat</v>
+        <v>/ənd,ən,n,ænd/</v>
       </c>
       <c r="C42" t="str">
-        <v>船</v>
+        <v>n./conj.</v>
       </c>
       <c r="D42" t="str">
-        <v>boat(船)📢</v>
+        <v>和</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>drunk</v>
       </c>
       <c r="B43" t="str">
-        <v>gold</v>
+        <v>/drʌŋk/</v>
       </c>
       <c r="C43" t="str">
-        <v>金色</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>gold(金色)📢</v>
+        <v>醉酒的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>dumb</v>
       </c>
       <c r="B44" t="str">
-        <v>slice</v>
+        <v>/dʌm/</v>
       </c>
       <c r="C44" t="str">
-        <v>切片</v>
+        <v>adj.</v>
       </c>
       <c r="D44" t="str">
-        <v>slice(切片)📢</v>
+        <v>哑的</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>vacuum</v>
       </c>
       <c r="B45" t="str">
-        <v>and</v>
+        <v>/ˈvækjuːm/</v>
       </c>
       <c r="C45" t="str">
-        <v>和</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D45" t="str">
-        <v>and(和)📢</v>
+        <v>真空</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>stem</v>
       </c>
       <c r="B46" t="str">
-        <v>drunk</v>
+        <v>/stem/</v>
       </c>
       <c r="C46" t="str">
-        <v>醉酒的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>drunk(醉酒的)📢</v>
+        <v>源于</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>conductor</v>
       </c>
       <c r="B47" t="str">
-        <v>disorder</v>
+        <v>/kənˈdʌktər/</v>
       </c>
       <c r="C47" t="str">
-        <v>混乱</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>disorder(混乱)📢</v>
+        <v>负责人</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>handful</v>
       </c>
       <c r="B48" t="str">
-        <v>dumb</v>
+        <v>/ˈhændfʊl/</v>
       </c>
       <c r="C48" t="str">
-        <v>哑的</v>
+        <v>n.</v>
       </c>
       <c r="D48" t="str">
-        <v>dumb(哑的)📢</v>
+        <v>一把</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>spill</v>
       </c>
       <c r="B49" t="str">
-        <v>extend</v>
+        <v>/spɪl/</v>
       </c>
       <c r="C49" t="str">
-        <v>延伸</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>extend(延伸)📢</v>
+        <v>溢出</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>blaze</v>
       </c>
       <c r="B50" t="str">
-        <v>vacuum</v>
+        <v>/bleɪz/</v>
       </c>
       <c r="C50" t="str">
-        <v>真空</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>vacuum(真空)📢</v>
+        <v>火焰</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>lie</v>
       </c>
       <c r="B51" t="str">
-        <v>stem</v>
+        <v>/laɪ/</v>
       </c>
       <c r="C51" t="str">
-        <v>源于</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D51" t="str">
-        <v>stem(源于)📢</v>
+        <v>谎言</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>beggar</v>
       </c>
       <c r="B52" t="str">
-        <v>conductor</v>
+        <v>/ˈbeɡər/</v>
       </c>
       <c r="C52" t="str">
-        <v>负责人</v>
+        <v>n./vt.</v>
       </c>
       <c r="D52" t="str">
-        <v>conductor(负责人)📢</v>
+        <v>乞丐</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>allow</v>
       </c>
       <c r="B53" t="str">
-        <v>handful</v>
+        <v>/əˈlaʊ/</v>
       </c>
       <c r="C53" t="str">
-        <v>一把</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D53" t="str">
-        <v>handful(一把)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>spill</v>
-      </c>
-      <c r="C54" t="str">
-        <v>溢出</v>
-      </c>
-      <c r="D54" t="str">
-        <v>spill(溢出)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>wage</v>
-      </c>
-      <c r="C55" t="str">
-        <v>工资</v>
-      </c>
-      <c r="D55" t="str">
-        <v>wage(工资)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>standard</v>
-      </c>
-      <c r="C56" t="str">
-        <v>标准</v>
-      </c>
-      <c r="D56" t="str">
-        <v>standard(标准)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>hazard</v>
-      </c>
-      <c r="C57" t="str">
-        <v>危险</v>
-      </c>
-      <c r="D57" t="str">
-        <v>hazard(危险)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>blaze</v>
-      </c>
-      <c r="C58" t="str">
-        <v>火焰</v>
-      </c>
-      <c r="D58" t="str">
-        <v>blaze(火焰)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>gold</v>
-      </c>
-      <c r="C59" t="str">
-        <v>金</v>
-      </c>
-      <c r="D59" t="str">
-        <v>gold(金)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>French</v>
-      </c>
-      <c r="C60" t="str">
-        <v>法国</v>
-      </c>
-      <c r="D60" t="str">
-        <v>French(法国)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>lie</v>
-      </c>
-      <c r="C61" t="str">
-        <v>谎言</v>
-      </c>
-      <c r="D61" t="str">
-        <v>lie(谎言)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>snowy</v>
-      </c>
-      <c r="C62" t="str">
-        <v>雪</v>
-      </c>
-      <c r="D62" t="str">
-        <v>snowy(雪)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>beggar</v>
-      </c>
-      <c r="C63" t="str">
-        <v>乞丐</v>
-      </c>
-      <c r="D63" t="str">
-        <v>beggar(乞丐)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>allow</v>
-      </c>
-      <c r="C64" t="str">
         <v>允许</v>
-      </c>
-      <c r="D64" t="str">
-        <v>allow(允许)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>critical</v>
-      </c>
-      <c r="C65" t="str">
-        <v>危急</v>
-      </c>
-      <c r="D65" t="str">
-        <v>critical(危急)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>generally</v>
-      </c>
-      <c r="C66" t="str">
-        <v>顺利</v>
-      </c>
-      <c r="D66" t="str">
-        <v>generally(顺利)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>staff</v>
-      </c>
-      <c r="C67" t="str">
-        <v>职员</v>
-      </c>
-      <c r="D67" t="str">
-        <v>staff(职员)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>gold</v>
-      </c>
-      <c r="C68" t="str">
-        <v>金</v>
-      </c>
-      <c r="D68" t="str">
-        <v>gold(金)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>hazard</v>
-      </c>
-      <c r="C69" t="str">
-        <v>风险</v>
-      </c>
-      <c r="D69" t="str">
-        <v>hazard(风险)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>